--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי פרץ - אהבה אמיתית</v>
+        <v>תומר מתנה - עלה לי רעיון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409612&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409617&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי פרץ - אהבה אמיתית</v>
+        <v>תומר מתנה - עלה לי רעיון</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עילאי אלמקייס - שוב פרידות</v>
+        <v>תאיר שדה - שרוטה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409611&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409616&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עילאי אלמקייס - שוב פרידות</v>
+        <v>תאיר שדה - שרוטה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נטע ברזילי - סרנדה</v>
+        <v>ששון שאולוב - אמא</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409610&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409615&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נטע ברזילי - סרנדה</v>
+        <v>ששון שאולוב - אמא</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נועם קלינשטיין - אותו דבר</v>
+        <v>שלומי שבת - ילדותי השניה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409609&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409614&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נועם קלינשטיין - אותו דבר</v>
+        <v>שלומי שבת - ילדותי השניה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>מאיה דדון - מסיבה עצובה</v>
+        <v>קובי פרץ - אוהב לנצח</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409608&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409613&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -621,164 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>מאיה דדון - מסיבה עצובה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יוסף חיים - לא אקרא לך מאמי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409607&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יוסף חיים - לא אקרא לך מאמי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>הראל מויאל - 1990</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409606&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>הראל מויאל - 1990</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>דיקלה - אין עוד מלבדך</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409605&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>דיקלה - אין עוד מלבדך</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אורי כלטוב &amp; רעות שי כהן - עשרים דקות</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409604&amp;sid=f0b6728b15c92b352360560d4b67e4a4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אורי כלטוב &amp; רעות שי כהן - עשרים דקות</v>
+        <v>קובי פרץ - אוהב לנצח</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תומר מתנה - עלה לי רעיון</v>
+        <v>עמית לואיס - עוד שנייה זה נגמר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409617&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409626&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-17</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תומר מתנה - עלה לי רעיון</v>
+        <v>עמית לואיס - עוד שנייה זה נגמר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תאיר שדה - שרוטה</v>
+        <v>עלמה גוב - בסיבוב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409616&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409625&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-17</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תאיר שדה - שרוטה</v>
+        <v>עלמה גוב - בסיבוב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ששון שאולוב - אמא</v>
+        <v>נועם בנאי - קנה סוכר</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409615&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409624&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-17</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ששון שאולוב - אמא</v>
+        <v>נועם בנאי - קנה סוכר</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שלומי שבת - ילדותי השניה</v>
+        <v>נוי דקל - אין לך אותי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409614&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409623&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-17</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שלומי שבת - ילדותי השניה</v>
+        <v>נוי דקל - אין לך אותי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>קובי פרץ - אוהב לנצח</v>
+        <v>לינוי טייב - אוויר לנשום</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409613&amp;sid=5fbe3a47cb84774c2a0004d5797c92fc</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409622&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-17</v>
@@ -621,12 +621,164 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>קובי פרץ - אוהב לנצח</v>
+        <v>לינוי טייב - אוויר לנשום</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יהודה נר - אל תדון</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409621&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יהודה נר - אל תדון</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409620&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>בני אלבז - אמריקה זה כאן</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409619&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>בני אלבז - אמריקה זה כאן</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409618&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-17</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמית לואיס - עוד שנייה זה נגמר</v>
+        <v>זהבי עם ליאור נרקיס - Aliya</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409626&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409634&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמית לואיס - עוד שנייה זה נגמר</v>
+        <v>זהבי עם ליאור נרקיס - Aliya</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עלמה גוב - בסיבוב</v>
+        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409625&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409633&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עלמה גוב - בסיבוב</v>
+        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נועם בנאי - קנה סוכר</v>
+        <v>דנה שלום כהן - כל בוקר לבחור</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409624&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409632&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נועם בנאי - קנה סוכר</v>
+        <v>דנה שלום כהן - כל בוקר לבחור</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>נוי דקל - אין לך אותי</v>
+        <v>דיז'ון - אפקט הדומינו</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409623&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409631&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>נוי דקל - אין לך אותי</v>
+        <v>דיז'ון - אפקט הדומינו</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לינוי טייב - אוויר לנשום</v>
+        <v>אסתר גד - הגעת לאן שהגעת</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409622&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409630&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>לינוי טייב - אוויר לנשום</v>
+        <v>אסתר גד - הגעת לאן שהגעת</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יהודה נר - אל תדון</v>
+        <v>אמיר אליהו - עוברים הם החיים</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409621&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409629&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יהודה נר - אל תדון</v>
+        <v>אמיר אליהו - עוברים הם החיים</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
+        <v>אור משה - לא מגיע לי</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409620&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409628&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ג'ירפות עם ליעם חכמון - טאם טאם</v>
+        <v>אור משה - לא מגיע לי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>בני אלבז - אמריקה זה כאן</v>
+        <v>אביר יעקב - בוגדת</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409619&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409627&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,50 +735,12 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>בני אלבז - אמריקה זה כאן</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409618&amp;sid=4c8ba2e28ad586784b4bb69b141405e7</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>בן ארצי &amp; אהרן רזאל - תודה</v>
+        <v>אביר יעקב - בוגדת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהבי עם ליאור נרקיס - Aliya</v>
+        <v>תמיר גל &amp; בני אלבז - מאמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409634&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409641&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-18</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהבי עם ליאור נרקיס - Aliya</v>
+        <v>תמיר גל &amp; בני אלבז - מאמי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
+        <v>שי עזאני - אורח</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409633&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409640&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-18</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הראל סקעת &amp; איתי גלו - כתוב על הקיר</v>
+        <v>שי עזאני - אורח</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דנה שלום כהן - כל בוקר לבחור</v>
+        <v>ריקיז - מלודי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409632&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409639&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-18</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דנה שלום כהן - כל בוקר לבחור</v>
+        <v>ריקיז - מלודי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>דיז'ון - אפקט הדומינו</v>
+        <v>נועה קירל - או לה פופה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409631&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409638&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-18</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>דיז'ון - אפקט הדומינו</v>
+        <v>נועה קירל - או לה פופה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אסתר גד - הגעת לאן שהגעת</v>
+        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409630&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409637&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-18</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אסתר גד - הגעת לאן שהגעת</v>
+        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אמיר אליהו - עוברים הם החיים</v>
+        <v>מור פדלון - חדש</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409629&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409636&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-18</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אמיר אליהו - עוברים הם החיים</v>
+        <v>מור פדלון - חדש</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אור משה - לא מגיע לי</v>
+        <v>מור מזרחי - הפסדת אותי</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-18</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409628&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409635&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-18</v>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אור משה - לא מגיע לי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביר יעקב - בוגדת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409627&amp;sid=68299f51413db2ec3bc66c335f4f09eb</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביר יעקב - בוגדת</v>
+        <v>מור מזרחי - הפסדת אותי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תמיר גל &amp; בני אלבז - מאמי</v>
+        <v>אביגיל - באתי להפתיע</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409641&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409642&amp;sid=15e82b1be007fa94d4ae04510603cc18</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,240 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תמיר גל &amp; בני אלבז - מאמי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שי עזאני - אורח</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409640&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שי עזאני - אורח</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ריקיז - מלודי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409639&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>ריקיז - מלודי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נועה קירל - או לה פופה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409638&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נועה קירל - או לה פופה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409637&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נהוראי תורג'מן - בתוך הראש שלי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מור פדלון - חדש</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409636&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מור פדלון - חדש</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>מור מזרחי - הפסדת אותי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409635&amp;sid=ac7fb72bb46c9b37363f8011434cf67e</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>מור מזרחי - הפסדת אותי</v>
+        <v>אביגיל - באתי להפתיע</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביגיל - באתי להפתיע</v>
+        <v>הדר הלל - צונאמי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409642&amp;sid=15e82b1be007fa94d4ae04510603cc18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409650&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביגיל - באתי להפתיע</v>
+        <v>הדר הלל - צונאמי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>דניאל בן חיים - לבד</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409649&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>דניאל בן חיים - לבד</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דון יצחק מזרחי - הולך באמונה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409648&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דון יצחק מזרחי - הולך באמונה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אפיק וקנין - יש לי כמה חלומות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409647&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אפיק וקנין - יש לי כמה חלומות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אליה והב - אבא סלח לי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409646&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אליה והב - אבא סלח לי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>איתי הררי - אישה יפה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409645&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>איתי הררי - אישה יפה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אייל טויטו - הלילה הזה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409644&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אייל טויטו - הלילה הזה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אופיר סלטון - איך אתה עוד כאן</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409643&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אופיר סלטון - איך אתה עוד כאן</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הדר הלל - צונאמי</v>
+        <v>נאור גור - מחשבות אסורות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409650&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409659&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הדר הלל - צונאמי</v>
+        <v>נאור גור - מחשבות אסורות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>דניאל בן חיים - לבד</v>
+        <v>מתן טולדנו - נותן הכל מהלב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409649&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409658&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>דניאל בן חיים - לבד</v>
+        <v>מתן טולדנו - נותן הכל מהלב</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דון יצחק מזרחי - הולך באמונה</v>
+        <v>מאיר אלפי - נוקאאוט</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409648&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409657&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דון יצחק מזרחי - הולך באמונה</v>
+        <v>מאיר אלפי - נוקאאוט</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אפיק וקנין - יש לי כמה חלומות</v>
+        <v>יחיאל שוקרון - התחלות חדשות</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409647&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409656&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אפיק וקנין - יש לי כמה חלומות</v>
+        <v>יחיאל שוקרון - התחלות חדשות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אליה והב - אבא סלח לי</v>
+        <v>יוסף כהן - לא טובה לי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409646&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409655&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-19</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אליה והב - אבא סלח לי</v>
+        <v>יוסף כהן - לא טובה לי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איתי הררי - אישה יפה</v>
+        <v>חיים דדון - מדורות בלב</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409645&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409654&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-19</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איתי הררי - אישה יפה</v>
+        <v>חיים דדון - מדורות בלב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אייל טויטו - הלילה הזה</v>
+        <v>חיים אל - להיות אני</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409644&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409653&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-19</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אייל טויטו - הלילה הזה</v>
+        <v>חיים אל - להיות אני</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אופיר סלטון - איך אתה עוד כאן</v>
+        <v>זיו אמסילי - היינו</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409643&amp;sid=c02426cfab6428db918c66ef60c4f097</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409652&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-19</v>
@@ -735,12 +735,50 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אופיר סלטון - איך אתה עוד כאן</v>
+        <v>זיו אמסילי - היינו</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>הדר שושן - תפילה של מישהו אחר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409651&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>הדר שושן - תפילה של מישהו אחר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נאור גור - מחשבות אסורות</v>
+        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409659&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409664&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נאור גור - מחשבות אסורות</v>
+        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מתן טולדנו - נותן הכל מהלב</v>
+        <v>שמעון טובול - אפור לבן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409658&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409663&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-19</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מתן טולדנו - נותן הכל מהלב</v>
+        <v>שמעון טובול - אפור לבן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מאיר אלפי - נוקאאוט</v>
+        <v>שלמה כהן - אמונה</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409657&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409662&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-19</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מאיר אלפי - נוקאאוט</v>
+        <v>שלמה כהן - אמונה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>יחיאל שוקרון - התחלות חדשות</v>
+        <v>עדן גבריאל - מה עשיתי לך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409656&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409661&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-19</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>יחיאל שוקרון - התחלות חדשות</v>
+        <v>עדן גבריאל - מה עשיתי לך</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסף כהן - לא טובה לי</v>
+        <v>נועה חלפון - ואולי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409655&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409660&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-19</v>
@@ -621,164 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסף כהן - לא טובה לי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>חיים דדון - מדורות בלב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409654&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>חיים דדון - מדורות בלב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>חיים אל - להיות אני</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409653&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>חיים אל - להיות אני</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>זיו אמסילי - היינו</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409652&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>זיו אמסילי - היינו</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>הדר שושן - תפילה של מישהו אחר</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409651&amp;sid=a42d983a94ea9b6e62915b47c09a4cd4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>הדר שושן - תפילה של מישהו אחר</v>
+        <v>נועה חלפון - ואולי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
+        <v>נועם בתן - מדאם</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409664&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=405155&amp;sid=539c4338e265962a6a59dd4295061feb</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון עוקשי &amp; ליאור מיארה - היא משקרת</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שמעון טובול - אפור לבן</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409663&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שמעון טובול - אפור לבן</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שלמה כהן - אמונה</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409662&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שלמה כהן - אמונה</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עדן גבריאל - מה עשיתי לך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409661&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עדן גבריאל - מה עשיתי לך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נועה חלפון - ואולי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409660&amp;sid=633c34665c2dadcaaeaccb47d4e14d24</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נועה חלפון - ואולי</v>
+        <v>נועם בתן - מדאם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועם בתן - מדאם</v>
+        <v>רונן לוגסי - מחרוזת שקטים 2026</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=405155&amp;sid=539c4338e265962a6a59dd4295061feb</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409702&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועם בתן - מדאם</v>
+        <v>רונן לוגסי - מחרוזת שקטים 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ראובן המלאך - מחרוזת השירים של פעם 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409701&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ראובן המלאך - מחרוזת השירים של פעם 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>פארידה - מחרוזת קווקזית 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409700&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פארידה - מחרוזת קווקזית 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ניראל ארגוב - מחרוזת פורים 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409699&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ניראל ארגוב - מחרוזת פורים 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נופר בטאט - מחרוזת טברנה 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409698&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נופר בטאט - מחרוזת טברנה 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>חיים אביטל - מחרוזת שקטים חלק א 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409697&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>חיים אביטל - מחרוזת שקטים חלק א 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>דודו קדוש - מחרוזת שקטים כבו הכוכבים 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409696&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>דודו קדוש - מחרוזת שקטים כבו הכוכבים 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>דודו בן חמו - מחרוזת מי שלא מוחא כפיים 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409695&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>דודו בן חמו - מחרוזת מי שלא מוחא כפיים 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אלינור חלילוב - מחרוזת 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409694&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אלינור חלילוב - מחרוזת 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>איציק הג'ינג'י - מחרוזת מאמי 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409693&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>איציק הג'ינג'י - מחרוזת מאמי 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>איציק הג'ינג'י - מחרוזת כאב ראש 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409692&amp;sid=5ffdf433b2b416922c8c99aa53dbe6cb</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-21</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>איציק הג'ינג'י - מחרוזת כאב ראש 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>